--- a/docs/planning/2. Sprint Timeplan - Tsering Lhamo Anodunkhartsang.xlsx
+++ b/docs/planning/2. Sprint Timeplan - Tsering Lhamo Anodunkhartsang.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/t.anodunkhartsang/projects/sovereign-ai-agent/docs/planning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8155473-4763-6947-A054-17B8A937C71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720111B6-0024-884C-806A-0805829B6DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34400" yWindow="600" windowWidth="34400" windowHeight="26860" xr2:uid="{AB7B3E1D-6C2A-9542-8379-0F3DD31EEDCF}"/>
+    <workbookView minimized="1" xWindow="68800" yWindow="9820" windowWidth="30240" windowHeight="18980" xr2:uid="{AB7B3E1D-6C2A-9542-8379-0F3DD31EEDCF}"/>
   </bookViews>
   <sheets>
     <sheet name="Timeplan" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="76">
   <si>
     <t>OOO</t>
   </si>
@@ -1455,99 +1455,182 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="75" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="65" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="46" fontId="5" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1557,89 +1640,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="75" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="60% - Accent1" xfId="2" builtinId="32"/>
@@ -1647,7 +1647,18 @@
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <color rgb="FF93C47D"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF93C47D"/>
+          <bgColor rgb="FF93C47D"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFE06666"/>
@@ -1759,22 +1770,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FFE06666"/>
       </font>
@@ -1830,32 +1825,10 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF93C47D"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF93C47D"/>
-          <bgColor rgb="FF93C47D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFEFEFEF"/>
           <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFE06666"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE06666"/>
-          <bgColor rgb="FFE06666"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1893,14 +1866,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEFEFEF"/>
-          <bgColor rgb="FFEFEFEF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FFE06666"/>
       </font>
@@ -1908,17 +1873,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFE06666"/>
           <bgColor rgb="FFE06666"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF93C47D"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF93C47D"/>
-          <bgColor rgb="FF93C47D"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2013,14 +1967,14 @@
     <xdr:from>
       <xdr:col>43</xdr:col>
       <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>43</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:colOff>108415</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2035,8 +1989,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13728700" y="850900"/>
-          <a:ext cx="0" cy="8445500"/>
+          <a:off x="13885746" y="895505"/>
+          <a:ext cx="6815" cy="8675958"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2387,7 +2341,7 @@
   <dimension ref="A1:BP55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="2.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.5" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="6.83203125" customWidth="1"/>
     <col min="4" max="4" width="9.1640625" customWidth="1"/>
@@ -2399,340 +2353,340 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:68" ht="19" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="78" t="s">
+      <c r="C1" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="78"/>
-      <c r="E1" s="79" t="s">
+      <c r="D1" s="83"/>
+      <c r="E1" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
-      <c r="Y1" s="79"/>
-      <c r="Z1" s="79"/>
-      <c r="AA1" s="79"/>
-      <c r="AB1" s="79"/>
-      <c r="AC1" s="79"/>
-      <c r="AD1" s="79"/>
-      <c r="AE1" s="79"/>
-      <c r="AF1" s="79"/>
-      <c r="AG1" s="79"/>
-      <c r="AH1" s="79"/>
-      <c r="AI1" s="79"/>
-      <c r="AJ1" s="79"/>
-      <c r="AK1" s="79"/>
-      <c r="AL1" s="79"/>
-      <c r="AM1" s="79"/>
-      <c r="AN1" s="79"/>
-      <c r="AO1" s="79"/>
-      <c r="AP1" s="79"/>
-      <c r="AQ1" s="79"/>
-      <c r="AR1" s="79"/>
-      <c r="AS1" s="118" t="s">
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
+      <c r="Z1" s="108"/>
+      <c r="AA1" s="108"/>
+      <c r="AB1" s="108"/>
+      <c r="AC1" s="108"/>
+      <c r="AD1" s="108"/>
+      <c r="AE1" s="108"/>
+      <c r="AF1" s="108"/>
+      <c r="AG1" s="108"/>
+      <c r="AH1" s="108"/>
+      <c r="AI1" s="108"/>
+      <c r="AJ1" s="108"/>
+      <c r="AK1" s="108"/>
+      <c r="AL1" s="108"/>
+      <c r="AM1" s="108"/>
+      <c r="AN1" s="108"/>
+      <c r="AO1" s="108"/>
+      <c r="AP1" s="108"/>
+      <c r="AQ1" s="108"/>
+      <c r="AR1" s="108"/>
+      <c r="AS1" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="AT1" s="119"/>
-      <c r="AU1" s="119"/>
-      <c r="AV1" s="119"/>
-      <c r="AW1" s="119"/>
-      <c r="AX1" s="119"/>
-      <c r="AY1" s="119"/>
-      <c r="AZ1" s="119"/>
-      <c r="BA1" s="119"/>
-      <c r="BB1" s="119"/>
-      <c r="BC1" s="119"/>
-      <c r="BD1" s="119"/>
-      <c r="BE1" s="119"/>
-      <c r="BF1" s="119"/>
-      <c r="BG1" s="119"/>
-      <c r="BH1" s="119"/>
-      <c r="BI1" s="119"/>
-      <c r="BJ1" s="119"/>
-      <c r="BK1" s="119"/>
-      <c r="BL1" s="119"/>
-      <c r="BM1" s="119"/>
-      <c r="BN1" s="119"/>
-      <c r="BO1" s="119"/>
-      <c r="BP1" s="120"/>
+      <c r="AT1" s="66"/>
+      <c r="AU1" s="66"/>
+      <c r="AV1" s="66"/>
+      <c r="AW1" s="66"/>
+      <c r="AX1" s="66"/>
+      <c r="AY1" s="66"/>
+      <c r="AZ1" s="66"/>
+      <c r="BA1" s="66"/>
+      <c r="BB1" s="66"/>
+      <c r="BC1" s="66"/>
+      <c r="BD1" s="66"/>
+      <c r="BE1" s="66"/>
+      <c r="BF1" s="66"/>
+      <c r="BG1" s="66"/>
+      <c r="BH1" s="66"/>
+      <c r="BI1" s="66"/>
+      <c r="BJ1" s="66"/>
+      <c r="BK1" s="66"/>
+      <c r="BL1" s="66"/>
+      <c r="BM1" s="66"/>
+      <c r="BN1" s="66"/>
+      <c r="BO1" s="66"/>
+      <c r="BP1" s="67"/>
     </row>
     <row r="2" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="74"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="91" t="s">
+      <c r="A2" s="104"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="116"/>
-      <c r="T2" s="116"/>
-      <c r="U2" s="91" t="s">
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="91"/>
-      <c r="W2" s="91"/>
-      <c r="X2" s="91"/>
-      <c r="Y2" s="91"/>
-      <c r="Z2" s="91"/>
-      <c r="AA2" s="91"/>
-      <c r="AB2" s="91"/>
-      <c r="AC2" s="91"/>
-      <c r="AD2" s="91"/>
-      <c r="AE2" s="91"/>
-      <c r="AF2" s="91"/>
-      <c r="AG2" s="91"/>
-      <c r="AH2" s="91"/>
-      <c r="AI2" s="91"/>
-      <c r="AJ2" s="91"/>
-      <c r="AK2" s="91"/>
-      <c r="AL2" s="91"/>
-      <c r="AM2" s="91"/>
-      <c r="AN2" s="91"/>
-      <c r="AO2" s="91"/>
-      <c r="AP2" s="91"/>
-      <c r="AQ2" s="91"/>
-      <c r="AR2" s="91"/>
-      <c r="AS2" s="91"/>
-      <c r="AT2" s="91"/>
-      <c r="AU2" s="91"/>
-      <c r="AV2" s="91"/>
-      <c r="AW2" s="91"/>
-      <c r="AX2" s="91"/>
-      <c r="AY2" s="91"/>
-      <c r="AZ2" s="91"/>
-      <c r="BA2" s="116"/>
-      <c r="BB2" s="116"/>
-      <c r="BC2" s="116"/>
-      <c r="BD2" s="116"/>
-      <c r="BE2" s="116"/>
-      <c r="BF2" s="116"/>
-      <c r="BG2" s="116"/>
-      <c r="BH2" s="116"/>
-      <c r="BI2" s="91" t="s">
+      <c r="V2" s="64"/>
+      <c r="W2" s="64"/>
+      <c r="X2" s="64"/>
+      <c r="Y2" s="64"/>
+      <c r="Z2" s="64"/>
+      <c r="AA2" s="64"/>
+      <c r="AB2" s="64"/>
+      <c r="AC2" s="64"/>
+      <c r="AD2" s="64"/>
+      <c r="AE2" s="64"/>
+      <c r="AF2" s="64"/>
+      <c r="AG2" s="64"/>
+      <c r="AH2" s="64"/>
+      <c r="AI2" s="64"/>
+      <c r="AJ2" s="64"/>
+      <c r="AK2" s="64"/>
+      <c r="AL2" s="64"/>
+      <c r="AM2" s="64"/>
+      <c r="AN2" s="64"/>
+      <c r="AO2" s="64"/>
+      <c r="AP2" s="64"/>
+      <c r="AQ2" s="64"/>
+      <c r="AR2" s="64"/>
+      <c r="AS2" s="64"/>
+      <c r="AT2" s="64"/>
+      <c r="AU2" s="64"/>
+      <c r="AV2" s="64"/>
+      <c r="AW2" s="64"/>
+      <c r="AX2" s="64"/>
+      <c r="AY2" s="64"/>
+      <c r="AZ2" s="64"/>
+      <c r="BA2" s="70"/>
+      <c r="BB2" s="70"/>
+      <c r="BC2" s="70"/>
+      <c r="BD2" s="70"/>
+      <c r="BE2" s="70"/>
+      <c r="BF2" s="70"/>
+      <c r="BG2" s="70"/>
+      <c r="BH2" s="70"/>
+      <c r="BI2" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="BJ2" s="91"/>
-      <c r="BK2" s="91"/>
-      <c r="BL2" s="91"/>
-      <c r="BM2" s="91"/>
-      <c r="BN2" s="91"/>
-      <c r="BO2" s="91"/>
-      <c r="BP2" s="91"/>
+      <c r="BJ2" s="64"/>
+      <c r="BK2" s="64"/>
+      <c r="BL2" s="64"/>
+      <c r="BM2" s="64"/>
+      <c r="BN2" s="64"/>
+      <c r="BO2" s="64"/>
+      <c r="BP2" s="64"/>
     </row>
     <row r="3" spans="1:68" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="74"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="92" t="s">
+      <c r="A3" s="104"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="113" t="s">
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="N3" s="114"/>
-      <c r="O3" s="114"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="114"/>
-      <c r="R3" s="114"/>
-      <c r="S3" s="114"/>
-      <c r="T3" s="115"/>
-      <c r="U3" s="103" t="s">
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="V3" s="104"/>
-      <c r="W3" s="104"/>
-      <c r="X3" s="104"/>
-      <c r="Y3" s="104"/>
-      <c r="Z3" s="104"/>
-      <c r="AA3" s="104"/>
-      <c r="AB3" s="105"/>
-      <c r="AC3" s="103" t="s">
+      <c r="V3" s="78"/>
+      <c r="W3" s="78"/>
+      <c r="X3" s="78"/>
+      <c r="Y3" s="78"/>
+      <c r="Z3" s="78"/>
+      <c r="AA3" s="78"/>
+      <c r="AB3" s="79"/>
+      <c r="AC3" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="AD3" s="104"/>
-      <c r="AE3" s="104"/>
-      <c r="AF3" s="104"/>
-      <c r="AG3" s="104"/>
-      <c r="AH3" s="104"/>
-      <c r="AI3" s="104"/>
-      <c r="AJ3" s="105"/>
-      <c r="AK3" s="103" t="s">
+      <c r="AD3" s="78"/>
+      <c r="AE3" s="78"/>
+      <c r="AF3" s="78"/>
+      <c r="AG3" s="78"/>
+      <c r="AH3" s="78"/>
+      <c r="AI3" s="78"/>
+      <c r="AJ3" s="79"/>
+      <c r="AK3" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="AL3" s="78"/>
-      <c r="AM3" s="78"/>
-      <c r="AN3" s="78"/>
-      <c r="AO3" s="78"/>
-      <c r="AP3" s="78"/>
-      <c r="AQ3" s="78"/>
-      <c r="AR3" s="108"/>
-      <c r="AS3" s="103" t="s">
+      <c r="AL3" s="83"/>
+      <c r="AM3" s="83"/>
+      <c r="AN3" s="83"/>
+      <c r="AO3" s="83"/>
+      <c r="AP3" s="83"/>
+      <c r="AQ3" s="83"/>
+      <c r="AR3" s="84"/>
+      <c r="AS3" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="AT3" s="104"/>
-      <c r="AU3" s="104"/>
-      <c r="AV3" s="104"/>
-      <c r="AW3" s="104"/>
-      <c r="AX3" s="104"/>
-      <c r="AY3" s="104"/>
-      <c r="AZ3" s="105"/>
-      <c r="BA3" s="113" t="s">
+      <c r="AT3" s="78"/>
+      <c r="AU3" s="78"/>
+      <c r="AV3" s="78"/>
+      <c r="AW3" s="78"/>
+      <c r="AX3" s="78"/>
+      <c r="AY3" s="78"/>
+      <c r="AZ3" s="79"/>
+      <c r="BA3" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="BB3" s="114"/>
-      <c r="BC3" s="114"/>
-      <c r="BD3" s="114"/>
-      <c r="BE3" s="114"/>
-      <c r="BF3" s="114"/>
-      <c r="BG3" s="114"/>
-      <c r="BH3" s="115"/>
-      <c r="BI3" s="103" t="s">
+      <c r="BB3" s="72"/>
+      <c r="BC3" s="72"/>
+      <c r="BD3" s="72"/>
+      <c r="BE3" s="72"/>
+      <c r="BF3" s="72"/>
+      <c r="BG3" s="72"/>
+      <c r="BH3" s="73"/>
+      <c r="BI3" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="BJ3" s="104"/>
-      <c r="BK3" s="104"/>
-      <c r="BL3" s="104"/>
-      <c r="BM3" s="104"/>
-      <c r="BN3" s="104"/>
-      <c r="BO3" s="104"/>
-      <c r="BP3" s="105"/>
+      <c r="BJ3" s="78"/>
+      <c r="BK3" s="78"/>
+      <c r="BL3" s="78"/>
+      <c r="BM3" s="78"/>
+      <c r="BN3" s="78"/>
+      <c r="BO3" s="78"/>
+      <c r="BP3" s="79"/>
     </row>
     <row r="4" spans="1:68" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="97" t="s">
+      <c r="A4" s="105"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="98"/>
-      <c r="E4" s="94" t="s">
+      <c r="D4" s="94"/>
+      <c r="E4" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="95"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="95"/>
-      <c r="L4" s="95"/>
-      <c r="M4" s="110" t="s">
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="111"/>
-      <c r="O4" s="111"/>
-      <c r="P4" s="111"/>
-      <c r="Q4" s="111"/>
-      <c r="R4" s="111"/>
-      <c r="S4" s="111"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="94" t="s">
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="76"/>
+      <c r="U4" s="80" t="s">
         <v>54</v>
       </c>
-      <c r="V4" s="106"/>
-      <c r="W4" s="106"/>
-      <c r="X4" s="106"/>
-      <c r="Y4" s="106"/>
-      <c r="Z4" s="106"/>
-      <c r="AA4" s="106"/>
-      <c r="AB4" s="107"/>
-      <c r="AC4" s="94" t="s">
+      <c r="V4" s="81"/>
+      <c r="W4" s="81"/>
+      <c r="X4" s="81"/>
+      <c r="Y4" s="81"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
+      <c r="AB4" s="82"/>
+      <c r="AC4" s="80" t="s">
         <v>56</v>
       </c>
-      <c r="AD4" s="106"/>
-      <c r="AE4" s="106"/>
-      <c r="AF4" s="106"/>
-      <c r="AG4" s="106"/>
-      <c r="AH4" s="106"/>
-      <c r="AI4" s="106"/>
-      <c r="AJ4" s="107"/>
-      <c r="AK4" s="94" t="s">
+      <c r="AD4" s="81"/>
+      <c r="AE4" s="81"/>
+      <c r="AF4" s="81"/>
+      <c r="AG4" s="81"/>
+      <c r="AH4" s="81"/>
+      <c r="AI4" s="81"/>
+      <c r="AJ4" s="82"/>
+      <c r="AK4" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="AL4" s="95"/>
-      <c r="AM4" s="95"/>
-      <c r="AN4" s="95"/>
-      <c r="AO4" s="95"/>
-      <c r="AP4" s="95"/>
-      <c r="AQ4" s="95"/>
-      <c r="AR4" s="109"/>
-      <c r="AS4" s="94" t="s">
+      <c r="AL4" s="85"/>
+      <c r="AM4" s="85"/>
+      <c r="AN4" s="85"/>
+      <c r="AO4" s="85"/>
+      <c r="AP4" s="85"/>
+      <c r="AQ4" s="85"/>
+      <c r="AR4" s="86"/>
+      <c r="AS4" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="AT4" s="106"/>
-      <c r="AU4" s="106"/>
-      <c r="AV4" s="106"/>
-      <c r="AW4" s="106"/>
-      <c r="AX4" s="106"/>
-      <c r="AY4" s="106"/>
-      <c r="AZ4" s="107"/>
-      <c r="BA4" s="110" t="s">
+      <c r="AT4" s="81"/>
+      <c r="AU4" s="81"/>
+      <c r="AV4" s="81"/>
+      <c r="AW4" s="81"/>
+      <c r="AX4" s="81"/>
+      <c r="AY4" s="81"/>
+      <c r="AZ4" s="82"/>
+      <c r="BA4" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="BB4" s="111"/>
-      <c r="BC4" s="111"/>
-      <c r="BD4" s="111"/>
-      <c r="BE4" s="111"/>
-      <c r="BF4" s="111"/>
-      <c r="BG4" s="111"/>
-      <c r="BH4" s="112"/>
-      <c r="BI4" s="94">
+      <c r="BB4" s="75"/>
+      <c r="BC4" s="75"/>
+      <c r="BD4" s="75"/>
+      <c r="BE4" s="75"/>
+      <c r="BF4" s="75"/>
+      <c r="BG4" s="75"/>
+      <c r="BH4" s="76"/>
+      <c r="BI4" s="80">
         <v>46084</v>
       </c>
-      <c r="BJ4" s="106"/>
-      <c r="BK4" s="106"/>
-      <c r="BL4" s="106"/>
-      <c r="BM4" s="106"/>
-      <c r="BN4" s="106"/>
-      <c r="BO4" s="106"/>
-      <c r="BP4" s="107"/>
+      <c r="BJ4" s="81"/>
+      <c r="BK4" s="81"/>
+      <c r="BL4" s="81"/>
+      <c r="BM4" s="81"/>
+      <c r="BN4" s="81"/>
+      <c r="BO4" s="81"/>
+      <c r="BP4" s="82"/>
     </row>
     <row r="5" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="89" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="21" t="s">
@@ -2810,8 +2764,8 @@
       <c r="BP5" s="18"/>
     </row>
     <row r="6" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A6" s="99"/>
-      <c r="B6" s="56"/>
+      <c r="A6" s="95"/>
+      <c r="B6" s="90"/>
       <c r="C6" s="22" t="s">
         <v>2</v>
       </c>
@@ -2887,8 +2841,8 @@
       <c r="BP6" s="6"/>
     </row>
     <row r="7" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A7" s="99"/>
-      <c r="B7" s="117" t="s">
+      <c r="A7" s="95"/>
+      <c r="B7" s="91" t="s">
         <v>72</v>
       </c>
       <c r="C7" s="21" t="s">
@@ -2966,8 +2920,8 @@
       <c r="BP7" s="3"/>
     </row>
     <row r="8" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="100"/>
-      <c r="B8" s="81"/>
+      <c r="A8" s="96"/>
+      <c r="B8" s="92"/>
       <c r="C8" s="23" t="s">
         <v>2</v>
       </c>
@@ -3043,10 +2997,10 @@
       <c r="BP8" s="15"/>
     </row>
     <row r="9" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="101" t="s">
+      <c r="B9" s="97" t="s">
         <v>67</v>
       </c>
       <c r="C9" s="21" t="s">
@@ -3126,8 +3080,8 @@
       <c r="BP9" s="53"/>
     </row>
     <row r="10" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="62"/>
-      <c r="B10" s="102"/>
+      <c r="A10" s="99"/>
+      <c r="B10" s="98"/>
       <c r="C10" s="23" t="s">
         <v>2</v>
       </c>
@@ -3205,8 +3159,8 @@
       <c r="BP10" s="50"/>
     </row>
     <row r="11" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A11" s="62"/>
-      <c r="B11" s="80" t="s">
+      <c r="A11" s="99"/>
+      <c r="B11" s="109" t="s">
         <v>20</v>
       </c>
       <c r="C11" s="21" t="s">
@@ -3294,14 +3248,14 @@
       </c>
     </row>
     <row r="12" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="63"/>
-      <c r="B12" s="81"/>
+      <c r="A12" s="100"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="30">
         <f>COUNTIF(E12:BP12,"i")/24</f>
-        <v>8.3333333333333329E-2</v>
+        <v>0.25</v>
       </c>
       <c r="E12" s="48"/>
       <c r="F12" s="49"/>
@@ -3338,7 +3292,9 @@
       <c r="AG12" s="49"/>
       <c r="AH12" s="49"/>
       <c r="AI12" s="49"/>
-      <c r="AJ12" s="49"/>
+      <c r="AJ12" s="49" t="s">
+        <v>17</v>
+      </c>
       <c r="AK12" s="48"/>
       <c r="AL12" s="49"/>
       <c r="AM12" s="49"/>
@@ -3346,7 +3302,9 @@
       <c r="AO12" s="49"/>
       <c r="AP12" s="49"/>
       <c r="AQ12" s="49"/>
-      <c r="AR12" s="49"/>
+      <c r="AR12" s="49" t="s">
+        <v>17</v>
+      </c>
       <c r="AS12" s="48"/>
       <c r="AT12" s="49"/>
       <c r="AU12" s="49"/>
@@ -3354,7 +3312,9 @@
       <c r="AW12" s="49"/>
       <c r="AX12" s="49"/>
       <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
+      <c r="AZ12" s="49" t="s">
+        <v>17</v>
+      </c>
       <c r="BA12" s="33"/>
       <c r="BB12" s="9"/>
       <c r="BC12" s="9"/>
@@ -3370,13 +3330,15 @@
       <c r="BM12" s="49"/>
       <c r="BN12" s="49"/>
       <c r="BO12" s="49"/>
-      <c r="BP12" s="15"/>
+      <c r="BP12" s="15" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A13" s="88" t="s">
+      <c r="A13" s="119" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="68" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="24" t="s">
@@ -3454,8 +3416,8 @@
       <c r="BP13" s="20"/>
     </row>
     <row r="14" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A14" s="89"/>
-      <c r="B14" s="57"/>
+      <c r="A14" s="120"/>
+      <c r="B14" s="117"/>
       <c r="C14" s="22" t="s">
         <v>2</v>
       </c>
@@ -3531,8 +3493,8 @@
       <c r="BP14" s="6"/>
     </row>
     <row r="15" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A15" s="89"/>
-      <c r="B15" s="58" t="s">
+      <c r="A15" s="120"/>
+      <c r="B15" s="118" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="21" t="s">
@@ -3610,8 +3572,8 @@
       <c r="BP15" s="3"/>
     </row>
     <row r="16" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="90"/>
-      <c r="B16" s="59"/>
+      <c r="A16" s="121"/>
+      <c r="B16" s="69"/>
       <c r="C16" s="23" t="s">
         <v>2</v>
       </c>
@@ -3687,10 +3649,10 @@
       <c r="BP16" s="15"/>
     </row>
     <row r="17" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="68" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="24" t="s">
@@ -3768,8 +3730,8 @@
       <c r="BP17" s="20"/>
     </row>
     <row r="18" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="61"/>
-      <c r="B18" s="59"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="69"/>
       <c r="C18" s="23" t="s">
         <v>2</v>
       </c>
@@ -3845,10 +3807,10 @@
       <c r="BP18" s="15"/>
     </row>
     <row r="19" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="68" t="s">
         <v>36</v>
       </c>
       <c r="C19" s="24" t="s">
@@ -3926,8 +3888,8 @@
       <c r="BP19" s="20"/>
     </row>
     <row r="20" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="61"/>
-      <c r="B20" s="59"/>
+      <c r="A20" s="57"/>
+      <c r="B20" s="69"/>
       <c r="C20" s="23" t="s">
         <v>2</v>
       </c>
@@ -4003,10 +3965,10 @@
       <c r="BP20" s="15"/>
     </row>
     <row r="21" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A21" s="62" t="s">
+      <c r="A21" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="55" t="s">
+      <c r="B21" s="68" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="25" t="s">
@@ -4084,8 +4046,8 @@
       <c r="BP21" s="20"/>
     </row>
     <row r="22" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A22" s="62"/>
-      <c r="B22" s="56"/>
+      <c r="A22" s="99"/>
+      <c r="B22" s="90"/>
       <c r="C22" s="22" t="s">
         <v>2</v>
       </c>
@@ -4161,8 +4123,8 @@
       <c r="BP22" s="6"/>
     </row>
     <row r="23" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A23" s="62"/>
-      <c r="B23" s="87" t="s">
+      <c r="A23" s="99"/>
+      <c r="B23" s="101" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="21" t="s">
@@ -4240,8 +4202,8 @@
       <c r="BP23" s="3"/>
     </row>
     <row r="24" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="63"/>
-      <c r="B24" s="59"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="69"/>
       <c r="C24" s="23" t="s">
         <v>2</v>
       </c>
@@ -4317,10 +4279,10 @@
       <c r="BP24" s="15"/>
     </row>
     <row r="25" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="68" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="24" t="s">
@@ -4400,8 +4362,8 @@
       <c r="BP25" s="20"/>
     </row>
     <row r="26" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A26" s="62"/>
-      <c r="B26" s="56"/>
+      <c r="A26" s="99"/>
+      <c r="B26" s="90"/>
       <c r="C26" s="22" t="s">
         <v>2</v>
       </c>
@@ -4479,8 +4441,8 @@
       <c r="BP26" s="6"/>
     </row>
     <row r="27" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A27" s="62"/>
-      <c r="B27" s="87" t="s">
+      <c r="A27" s="99"/>
+      <c r="B27" s="101" t="s">
         <v>41</v>
       </c>
       <c r="C27" s="21" t="s">
@@ -4560,8 +4522,8 @@
       <c r="BP27" s="3"/>
     </row>
     <row r="28" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="63"/>
-      <c r="B28" s="59"/>
+      <c r="A28" s="100"/>
+      <c r="B28" s="69"/>
       <c r="C28" s="23" t="s">
         <v>2</v>
       </c>
@@ -4639,10 +4601,10 @@
       <c r="BP28" s="15"/>
     </row>
     <row r="29" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A29" s="60" t="s">
+      <c r="A29" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="68" t="s">
         <v>42</v>
       </c>
       <c r="C29" s="24" t="s">
@@ -4720,8 +4682,8 @@
       <c r="BP29" s="20"/>
     </row>
     <row r="30" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="61"/>
-      <c r="B30" s="59"/>
+      <c r="A30" s="57"/>
+      <c r="B30" s="69"/>
       <c r="C30" s="23" t="s">
         <v>2</v>
       </c>
@@ -4797,10 +4759,10 @@
       <c r="BP30" s="15"/>
     </row>
     <row r="31" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A31" s="60" t="s">
+      <c r="A31" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="68" t="s">
         <v>44</v>
       </c>
       <c r="C31" s="24" t="s">
@@ -4880,8 +4842,8 @@
       <c r="BP31" s="20"/>
     </row>
     <row r="32" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A32" s="62"/>
-      <c r="B32" s="56"/>
+      <c r="A32" s="99"/>
+      <c r="B32" s="90"/>
       <c r="C32" s="22" t="s">
         <v>2</v>
       </c>
@@ -4959,8 +4921,8 @@
       <c r="BP32" s="6"/>
     </row>
     <row r="33" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A33" s="62"/>
-      <c r="B33" s="87" t="s">
+      <c r="A33" s="99"/>
+      <c r="B33" s="101" t="s">
         <v>45</v>
       </c>
       <c r="C33" s="21" t="s">
@@ -5038,14 +5000,14 @@
       <c r="BP33" s="3"/>
     </row>
     <row r="34" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="63"/>
-      <c r="B34" s="59"/>
+      <c r="A34" s="100"/>
+      <c r="B34" s="69"/>
       <c r="C34" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D34" s="29">
         <f>COUNTIF(E34:BP34,"i")/24</f>
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="E34" s="13"/>
       <c r="F34" s="14"/>
@@ -5073,7 +5035,9 @@
       <c r="AB34" s="15"/>
       <c r="AC34" s="13"/>
       <c r="AD34" s="14"/>
-      <c r="AE34" s="14"/>
+      <c r="AE34" s="14" t="s">
+        <v>17</v>
+      </c>
       <c r="AF34" s="14"/>
       <c r="AG34" s="14"/>
       <c r="AH34" s="14"/>
@@ -5113,10 +5077,10 @@
       <c r="BP34" s="15"/>
     </row>
     <row r="35" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A35" s="60" t="s">
+      <c r="A35" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="55" t="s">
+      <c r="B35" s="68" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="24" t="s">
@@ -5198,14 +5162,14 @@
       <c r="BP35" s="20"/>
     </row>
     <row r="36" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="61"/>
-      <c r="B36" s="59"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="69"/>
       <c r="C36" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D36" s="30">
         <f>COUNTIF(E36:BP36,"i")/24</f>
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="14"/>
@@ -5234,9 +5198,15 @@
       <c r="AC36" s="13"/>
       <c r="AD36" s="14"/>
       <c r="AE36" s="14"/>
-      <c r="AF36" s="14"/>
-      <c r="AG36" s="14"/>
-      <c r="AH36" s="14"/>
+      <c r="AF36" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG36" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH36" s="14" t="s">
+        <v>17</v>
+      </c>
       <c r="AI36" s="14"/>
       <c r="AJ36" s="15"/>
       <c r="AK36" s="13"/>
@@ -5273,10 +5243,10 @@
       <c r="BP36" s="15"/>
     </row>
     <row r="37" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A37" s="60" t="s">
+      <c r="A37" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="B37" s="55" t="s">
+      <c r="B37" s="68" t="s">
         <v>47</v>
       </c>
       <c r="C37" s="24" t="s">
@@ -5356,14 +5326,14 @@
       <c r="BP37" s="20"/>
     </row>
     <row r="38" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="61"/>
-      <c r="B38" s="59"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="69"/>
       <c r="C38" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="29">
         <f>COUNTIF(E38:BP38,"i")/24</f>
-        <v>0</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="14"/>
@@ -5395,8 +5365,12 @@
       <c r="AF38" s="14"/>
       <c r="AG38" s="14"/>
       <c r="AH38" s="14"/>
-      <c r="AI38" s="14"/>
-      <c r="AJ38" s="14"/>
+      <c r="AI38" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ38" s="14" t="s">
+        <v>17</v>
+      </c>
       <c r="AK38" s="13"/>
       <c r="AL38" s="14"/>
       <c r="AM38" s="14"/>
@@ -5431,10 +5405,10 @@
       <c r="BP38" s="15"/>
     </row>
     <row r="39" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A39" s="60" t="s">
+      <c r="A39" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="55" t="s">
+      <c r="B39" s="68" t="s">
         <v>49</v>
       </c>
       <c r="C39" s="24" t="s">
@@ -5518,14 +5492,14 @@
       <c r="BP39" s="20"/>
     </row>
     <row r="40" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A40" s="62"/>
-      <c r="B40" s="56"/>
+      <c r="A40" s="99"/>
+      <c r="B40" s="90"/>
       <c r="C40" s="22" t="s">
         <v>2</v>
       </c>
       <c r="D40" s="30">
         <f>COUNTIF(E40:BP40,"i")/24</f>
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="5"/>
@@ -5559,10 +5533,18 @@
       <c r="AH40" s="5"/>
       <c r="AI40" s="5"/>
       <c r="AJ40" s="6"/>
-      <c r="AK40" s="7"/>
-      <c r="AL40" s="5"/>
-      <c r="AM40" s="5"/>
-      <c r="AN40" s="5"/>
+      <c r="AK40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL40" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM40" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN40" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="AO40" s="5"/>
       <c r="AP40" s="5"/>
       <c r="AQ40" s="5"/>
@@ -5593,8 +5575,8 @@
       <c r="BP40" s="6"/>
     </row>
     <row r="41" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A41" s="62"/>
-      <c r="B41" s="87" t="s">
+      <c r="A41" s="99"/>
+      <c r="B41" s="101" t="s">
         <v>50</v>
       </c>
       <c r="C41" s="21" t="s">
@@ -5674,14 +5656,14 @@
       <c r="BP41" s="3"/>
     </row>
     <row r="42" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="63"/>
-      <c r="B42" s="59"/>
+      <c r="A42" s="100"/>
+      <c r="B42" s="69"/>
       <c r="C42" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D42" s="29">
         <f>COUNTIF(E42:BP42,"i")/24</f>
-        <v>0</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="E42" s="13"/>
       <c r="F42" s="14"/>
@@ -5719,8 +5701,12 @@
       <c r="AL42" s="14"/>
       <c r="AM42" s="14"/>
       <c r="AN42" s="14"/>
-      <c r="AO42" s="14"/>
-      <c r="AP42" s="14"/>
+      <c r="AO42" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP42" s="14" t="s">
+        <v>17</v>
+      </c>
       <c r="AQ42" s="14"/>
       <c r="AR42" s="15"/>
       <c r="AS42" s="13"/>
@@ -5749,10 +5735,10 @@
       <c r="BP42" s="15"/>
     </row>
     <row r="43" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A43" s="60" t="s">
+      <c r="A43" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="B43" s="55" t="s">
+      <c r="B43" s="68" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="24" t="s">
@@ -5830,14 +5816,14 @@
       <c r="BP43" s="20"/>
     </row>
     <row r="44" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="61"/>
-      <c r="B44" s="59"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="69"/>
       <c r="C44" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D44" s="30">
         <f>COUNTIF(E44:BP44,"i")/24</f>
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="14"/>
@@ -5877,7 +5863,9 @@
       <c r="AN44" s="14"/>
       <c r="AO44" s="14"/>
       <c r="AP44" s="14"/>
-      <c r="AQ44" s="14"/>
+      <c r="AQ44" s="14" t="s">
+        <v>17</v>
+      </c>
       <c r="AR44" s="15"/>
       <c r="AS44" s="13"/>
       <c r="AT44" s="14"/>
@@ -5905,10 +5893,10 @@
       <c r="BP44" s="15"/>
     </row>
     <row r="45" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A45" s="60" t="s">
+      <c r="A45" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="55" t="s">
+      <c r="B45" s="68" t="s">
         <v>65</v>
       </c>
       <c r="C45" s="24" t="s">
@@ -5986,14 +5974,14 @@
       <c r="BP45" s="12"/>
     </row>
     <row r="46" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="61"/>
-      <c r="B46" s="59"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="69"/>
       <c r="C46" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D46" s="29">
         <f>COUNTIF(E46:BP46,"i")/24</f>
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="E46" s="13"/>
       <c r="F46" s="14"/>
@@ -6034,7 +6022,9 @@
       <c r="AO46" s="14"/>
       <c r="AP46" s="14"/>
       <c r="AQ46" s="14"/>
-      <c r="AR46" s="15"/>
+      <c r="AR46" s="15" t="s">
+        <v>17</v>
+      </c>
       <c r="AS46" s="13"/>
       <c r="AT46" s="14"/>
       <c r="AU46" s="14"/>
@@ -6061,10 +6051,10 @@
       <c r="BP46" s="15"/>
     </row>
     <row r="47" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A47" s="60" t="s">
+      <c r="A47" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="B47" s="55" t="s">
+      <c r="B47" s="68" t="s">
         <v>69</v>
       </c>
       <c r="C47" s="24" t="s">
@@ -6168,14 +6158,14 @@
       <c r="BP47" s="12"/>
     </row>
     <row r="48" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="61"/>
-      <c r="B48" s="59"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="69"/>
       <c r="C48" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D48" s="29">
         <f>COUNTIF(E48:BP48,"i")/24</f>
-        <v>0</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="E48" s="13"/>
       <c r="F48" s="14"/>
@@ -6217,13 +6207,27 @@
       <c r="AP48" s="14"/>
       <c r="AQ48" s="14"/>
       <c r="AR48" s="15"/>
-      <c r="AS48" s="13"/>
-      <c r="AT48" s="14"/>
-      <c r="AU48" s="14"/>
-      <c r="AV48" s="14"/>
-      <c r="AW48" s="14"/>
-      <c r="AX48" s="14"/>
-      <c r="AY48" s="14"/>
+      <c r="AS48" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AW48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AX48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY48" s="14" t="s">
+        <v>17</v>
+      </c>
       <c r="AZ48" s="15"/>
       <c r="BA48" s="33"/>
       <c r="BB48" s="9"/>
@@ -6233,20 +6237,34 @@
       <c r="BF48" s="9"/>
       <c r="BG48" s="9"/>
       <c r="BH48" s="34"/>
-      <c r="BI48" s="13"/>
-      <c r="BJ48" s="14"/>
-      <c r="BK48" s="14"/>
-      <c r="BL48" s="14"/>
-      <c r="BM48" s="14"/>
-      <c r="BN48" s="14"/>
-      <c r="BO48" s="14"/>
+      <c r="BI48" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="BJ48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="BK48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="BL48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="BM48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="BN48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="BO48" s="14" t="s">
+        <v>17</v>
+      </c>
       <c r="BP48" s="15"/>
     </row>
     <row r="49" spans="1:68" x14ac:dyDescent="0.2">
-      <c r="A49" s="82" t="s">
+      <c r="A49" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="82"/>
+      <c r="B49" s="110"/>
       <c r="C49" s="24" t="s">
         <v>8</v>
       </c>
@@ -6254,17 +6272,17 @@
         <f>SUMIF($C$5:$C$48,"should",$D$5:$D$48)</f>
         <v>2.125</v>
       </c>
-      <c r="E49" s="66">
+      <c r="E49" s="58">
         <f>COUNTIF(E5:L46,"s")/24</f>
         <v>0.375</v>
       </c>
-      <c r="F49" s="67"/>
-      <c r="G49" s="67"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="67"/>
-      <c r="J49" s="67"/>
-      <c r="K49" s="67"/>
-      <c r="L49" s="68"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="59"/>
+      <c r="K49" s="59"/>
+      <c r="L49" s="60"/>
       <c r="M49" s="33"/>
       <c r="N49" s="9"/>
       <c r="O49" s="9"/>
@@ -6273,50 +6291,50 @@
       <c r="R49" s="9"/>
       <c r="S49" s="9"/>
       <c r="T49" s="34"/>
-      <c r="U49" s="66">
+      <c r="U49" s="58">
         <f>COUNTIF(U5:AB46,"s")/24</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="V49" s="67"/>
-      <c r="W49" s="67"/>
-      <c r="X49" s="67"/>
-      <c r="Y49" s="67"/>
-      <c r="Z49" s="67"/>
-      <c r="AA49" s="67"/>
-      <c r="AB49" s="68"/>
-      <c r="AC49" s="66">
+      <c r="V49" s="59"/>
+      <c r="W49" s="59"/>
+      <c r="X49" s="59"/>
+      <c r="Y49" s="59"/>
+      <c r="Z49" s="59"/>
+      <c r="AA49" s="59"/>
+      <c r="AB49" s="60"/>
+      <c r="AC49" s="58">
         <f>COUNTIF(AC5:AJ48,"s")/24</f>
         <v>0.375</v>
       </c>
-      <c r="AD49" s="67"/>
-      <c r="AE49" s="67"/>
-      <c r="AF49" s="67"/>
-      <c r="AG49" s="67"/>
-      <c r="AH49" s="67"/>
-      <c r="AI49" s="67"/>
-      <c r="AJ49" s="68"/>
-      <c r="AK49" s="66">
+      <c r="AD49" s="59"/>
+      <c r="AE49" s="59"/>
+      <c r="AF49" s="59"/>
+      <c r="AG49" s="59"/>
+      <c r="AH49" s="59"/>
+      <c r="AI49" s="59"/>
+      <c r="AJ49" s="60"/>
+      <c r="AK49" s="58">
         <f>COUNTIF(AK5:AR48,"s")/24</f>
         <v>0.375</v>
       </c>
-      <c r="AL49" s="67"/>
-      <c r="AM49" s="67"/>
-      <c r="AN49" s="67"/>
-      <c r="AO49" s="67"/>
-      <c r="AP49" s="67"/>
-      <c r="AQ49" s="67"/>
-      <c r="AR49" s="68"/>
-      <c r="AS49" s="66">
+      <c r="AL49" s="59"/>
+      <c r="AM49" s="59"/>
+      <c r="AN49" s="59"/>
+      <c r="AO49" s="59"/>
+      <c r="AP49" s="59"/>
+      <c r="AQ49" s="59"/>
+      <c r="AR49" s="60"/>
+      <c r="AS49" s="58">
         <f>COUNTIF(AS5:AZ48,"s")/24</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AT49" s="67"/>
-      <c r="AU49" s="67"/>
-      <c r="AV49" s="67"/>
-      <c r="AW49" s="67"/>
-      <c r="AX49" s="67"/>
-      <c r="AY49" s="67"/>
-      <c r="AZ49" s="68"/>
+      <c r="AT49" s="59"/>
+      <c r="AU49" s="59"/>
+      <c r="AV49" s="59"/>
+      <c r="AW49" s="59"/>
+      <c r="AX49" s="59"/>
+      <c r="AY49" s="59"/>
+      <c r="AZ49" s="60"/>
       <c r="BA49" s="33"/>
       <c r="BB49" s="9"/>
       <c r="BC49" s="9"/>
@@ -6325,39 +6343,39 @@
       <c r="BF49" s="9"/>
       <c r="BG49" s="9"/>
       <c r="BH49" s="34"/>
-      <c r="BI49" s="66">
+      <c r="BI49" s="58">
         <f>COUNTIF(BI5:BP48,"s")/24</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="BJ49" s="67"/>
-      <c r="BK49" s="67"/>
-      <c r="BL49" s="67"/>
-      <c r="BM49" s="67"/>
-      <c r="BN49" s="67"/>
-      <c r="BO49" s="67"/>
-      <c r="BP49" s="68"/>
+      <c r="BJ49" s="59"/>
+      <c r="BK49" s="59"/>
+      <c r="BL49" s="59"/>
+      <c r="BM49" s="59"/>
+      <c r="BN49" s="59"/>
+      <c r="BO49" s="59"/>
+      <c r="BP49" s="60"/>
     </row>
     <row r="50" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="83"/>
-      <c r="B50" s="83"/>
+      <c r="A50" s="111"/>
+      <c r="B50" s="111"/>
       <c r="C50" s="23" t="s">
         <v>2</v>
       </c>
       <c r="D50" s="45">
         <f>SUMIF($C$5:$C$48,"Is",$D$5:$D$48)</f>
-        <v>0.79166666666666685</v>
-      </c>
-      <c r="E50" s="84">
+        <v>2.125</v>
+      </c>
+      <c r="E50" s="112">
         <f>COUNTIF(E5:L48,"i")/24</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="F50" s="85"/>
-      <c r="G50" s="85"/>
-      <c r="H50" s="85"/>
-      <c r="I50" s="85"/>
-      <c r="J50" s="85"/>
-      <c r="K50" s="85"/>
-      <c r="L50" s="86"/>
+      <c r="F50" s="113"/>
+      <c r="G50" s="113"/>
+      <c r="H50" s="113"/>
+      <c r="I50" s="113"/>
+      <c r="J50" s="113"/>
+      <c r="K50" s="113"/>
+      <c r="L50" s="114"/>
       <c r="M50" s="35"/>
       <c r="N50" s="36"/>
       <c r="O50" s="36"/>
@@ -6366,50 +6384,50 @@
       <c r="R50" s="36"/>
       <c r="S50" s="36"/>
       <c r="T50" s="37"/>
-      <c r="U50" s="69">
+      <c r="U50" s="61">
         <f>COUNTIF(U5:AB48,"i")/24</f>
         <v>0.375</v>
       </c>
-      <c r="V50" s="70"/>
-      <c r="W50" s="70"/>
-      <c r="X50" s="70"/>
-      <c r="Y50" s="70"/>
-      <c r="Z50" s="70"/>
-      <c r="AA50" s="70"/>
-      <c r="AB50" s="71"/>
-      <c r="AC50" s="69">
+      <c r="V50" s="62"/>
+      <c r="W50" s="62"/>
+      <c r="X50" s="62"/>
+      <c r="Y50" s="62"/>
+      <c r="Z50" s="62"/>
+      <c r="AA50" s="62"/>
+      <c r="AB50" s="63"/>
+      <c r="AC50" s="61">
         <f>COUNTIF(AC5:AJ48,"i")/24</f>
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="AD50" s="70"/>
-      <c r="AE50" s="70"/>
-      <c r="AF50" s="70"/>
-      <c r="AG50" s="70"/>
-      <c r="AH50" s="70"/>
-      <c r="AI50" s="70"/>
-      <c r="AJ50" s="71"/>
-      <c r="AK50" s="69">
+        <v>0.375</v>
+      </c>
+      <c r="AD50" s="62"/>
+      <c r="AE50" s="62"/>
+      <c r="AF50" s="62"/>
+      <c r="AG50" s="62"/>
+      <c r="AH50" s="62"/>
+      <c r="AI50" s="62"/>
+      <c r="AJ50" s="63"/>
+      <c r="AK50" s="61">
         <f>COUNTIF(AK5:AR48,"i")/24</f>
-        <v>0</v>
-      </c>
-      <c r="AL50" s="70"/>
-      <c r="AM50" s="70"/>
-      <c r="AN50" s="70"/>
-      <c r="AO50" s="70"/>
-      <c r="AP50" s="70"/>
-      <c r="AQ50" s="70"/>
-      <c r="AR50" s="71"/>
-      <c r="AS50" s="69">
+        <v>0.375</v>
+      </c>
+      <c r="AL50" s="62"/>
+      <c r="AM50" s="62"/>
+      <c r="AN50" s="62"/>
+      <c r="AO50" s="62"/>
+      <c r="AP50" s="62"/>
+      <c r="AQ50" s="62"/>
+      <c r="AR50" s="63"/>
+      <c r="AS50" s="61">
         <f>COUNTIF(AS5:AZ48,"i")/24</f>
-        <v>0</v>
-      </c>
-      <c r="AT50" s="70"/>
-      <c r="AU50" s="70"/>
-      <c r="AV50" s="70"/>
-      <c r="AW50" s="70"/>
-      <c r="AX50" s="70"/>
-      <c r="AY50" s="70"/>
-      <c r="AZ50" s="71"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AT50" s="62"/>
+      <c r="AU50" s="62"/>
+      <c r="AV50" s="62"/>
+      <c r="AW50" s="62"/>
+      <c r="AX50" s="62"/>
+      <c r="AY50" s="62"/>
+      <c r="AZ50" s="63"/>
       <c r="BA50" s="35"/>
       <c r="BB50" s="36"/>
       <c r="BC50" s="36"/>
@@ -6418,40 +6436,40 @@
       <c r="BF50" s="36"/>
       <c r="BG50" s="36"/>
       <c r="BH50" s="37"/>
-      <c r="BI50" s="69">
+      <c r="BI50" s="61">
         <f>COUNTIF(BI5:BP48,"i")/24</f>
-        <v>0</v>
-      </c>
-      <c r="BJ50" s="70"/>
-      <c r="BK50" s="70"/>
-      <c r="BL50" s="70"/>
-      <c r="BM50" s="70"/>
-      <c r="BN50" s="70"/>
-      <c r="BO50" s="70"/>
-      <c r="BP50" s="71"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="BJ50" s="62"/>
+      <c r="BK50" s="62"/>
+      <c r="BL50" s="62"/>
+      <c r="BM50" s="62"/>
+      <c r="BN50" s="62"/>
+      <c r="BO50" s="62"/>
+      <c r="BP50" s="63"/>
     </row>
     <row r="51" spans="1:68" x14ac:dyDescent="0.2">
       <c r="E51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F51" s="64" t="s">
+      <c r="F51" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="G51" s="65"/>
+      <c r="G51" s="116"/>
       <c r="I51" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="64" t="s">
+      <c r="J51" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="K51" s="65"/>
+      <c r="K51" s="116"/>
     </row>
     <row r="52" spans="1:68" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="1:68" ht="19" x14ac:dyDescent="0.25">
-      <c r="A53" s="72" t="s">
+      <c r="A53" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="B53" s="73"/>
+      <c r="B53" s="103"/>
     </row>
     <row r="54" spans="1:68" x14ac:dyDescent="0.2">
       <c r="A54" s="46" t="s">
@@ -6471,6 +6489,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="AC49:AJ49"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="AK49:AR49"/>
+    <mergeCell ref="AC50:AJ50"/>
+    <mergeCell ref="AK50:AR50"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:AR1"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A49:B50"/>
+    <mergeCell ref="E49:L49"/>
+    <mergeCell ref="E50:L50"/>
+    <mergeCell ref="U49:AB49"/>
+    <mergeCell ref="U50:AB50"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E3:L3"/>
+    <mergeCell ref="E4:L4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AC3:AJ3"/>
+    <mergeCell ref="AC4:AJ4"/>
+    <mergeCell ref="AK3:AR3"/>
+    <mergeCell ref="AK4:AR4"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="M4:T4"/>
+    <mergeCell ref="U4:AB4"/>
+    <mergeCell ref="M3:T3"/>
+    <mergeCell ref="U3:AB3"/>
+    <mergeCell ref="M2:T2"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="BI49:BP49"/>
     <mergeCell ref="BI50:BP50"/>
@@ -6487,183 +6569,96 @@
     <mergeCell ref="AS49:AZ49"/>
     <mergeCell ref="AS50:AZ50"/>
     <mergeCell ref="U2:AZ2"/>
-    <mergeCell ref="M4:T4"/>
-    <mergeCell ref="U4:AB4"/>
-    <mergeCell ref="M3:T3"/>
-    <mergeCell ref="U3:AB3"/>
-    <mergeCell ref="M2:T2"/>
-    <mergeCell ref="AC3:AJ3"/>
-    <mergeCell ref="AC4:AJ4"/>
-    <mergeCell ref="AK3:AR3"/>
-    <mergeCell ref="AK4:AR4"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="E3:L3"/>
-    <mergeCell ref="E4:L4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A25:A28"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="AK49:AR49"/>
-    <mergeCell ref="AC50:AJ50"/>
-    <mergeCell ref="AK50:AR50"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:AR1"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A49:B50"/>
-    <mergeCell ref="E49:L49"/>
-    <mergeCell ref="E50:L50"/>
-    <mergeCell ref="U49:AB49"/>
-    <mergeCell ref="U50:AB50"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="AC49:AJ49"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="E3:E4">
-    <cfRule type="expression" dxfId="26" priority="149">
+    <cfRule type="expression" dxfId="21" priority="149">
       <formula>LEFT(E$3, 3)&lt;&gt;"Tag"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E49:E51 U5:AR8 E5:L48 U10:AR46 U47:AZ48">
-    <cfRule type="containsText" dxfId="5" priority="78" operator="containsText" text="s">
+  <conditionalFormatting sqref="E5:L48 E49:E51">
+    <cfRule type="cellIs" dxfId="20" priority="79" operator="equal">
+      <formula>"i"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="19" priority="78" operator="containsText" text="s">
       <formula>NOT(ISERROR(SEARCH(("s"),(E5))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="79" operator="equal">
-      <formula>"i"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I51">
-    <cfRule type="containsText" dxfId="25" priority="76" operator="containsText" text="s">
+    <cfRule type="cellIs" dxfId="18" priority="77" operator="equal">
+      <formula>"i"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="17" priority="76" operator="containsText" text="s">
       <formula>NOT(ISERROR(SEARCH(("s"),(I51))))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="77" operator="equal">
-      <formula>"i"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:AR4">
-    <cfRule type="expression" dxfId="23" priority="146">
+  <conditionalFormatting sqref="M3:BP4">
+    <cfRule type="expression" dxfId="16" priority="9">
       <formula>LEFT(M$3, 3)&lt;&gt;"Tag"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U49:U50 AC49:AC50 AK49:AK50">
-    <cfRule type="containsText" dxfId="22" priority="90" operator="containsText" text="s">
+    <cfRule type="cellIs" dxfId="15" priority="91" operator="equal">
+      <formula>"i"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="90" operator="containsText" text="s">
       <formula>NOT(ISERROR(SEARCH(("s"),(U49))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="91" operator="equal">
-      <formula>"i"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U9:AB9">
-    <cfRule type="containsText" dxfId="20" priority="140" operator="containsText" text="s">
+    <cfRule type="cellIs" dxfId="13" priority="141" operator="equal">
+      <formula>"i"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="140" operator="containsText" text="s">
       <formula>NOT(ISERROR(SEARCH(("s"),(U9))))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="141" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U5:AZ8">
+    <cfRule type="cellIs" dxfId="11" priority="16" operator="equal">
       <formula>"i"</formula>
     </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="15" operator="containsText" text="s">
+      <formula>NOT(ISERROR(SEARCH(("s"),(U5))))</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS3:AZ4">
-    <cfRule type="expression" dxfId="18" priority="17">
-      <formula>LEFT(AS$3, 3)&lt;&gt;"Tag"</formula>
+  <conditionalFormatting sqref="U10:AZ48">
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"i"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="s">
+      <formula>NOT(ISERROR(SEARCH(("s"),(U10))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS49:AS50">
-    <cfRule type="containsText" dxfId="17" priority="11" operator="containsText" text="s">
-      <formula>NOT(ISERROR(SEARCH(("s"),(AS49))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
       <formula>"i"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AS5:AZ8">
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="s">
-      <formula>NOT(ISERROR(SEARCH(("s"),(AS5))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
-      <formula>"i"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AS10:AZ46">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="s">
-      <formula>NOT(ISERROR(SEARCH(("s"),(AS10))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
-      <formula>"i"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BA3:BH4">
-    <cfRule type="expression" dxfId="11" priority="10">
-      <formula>LEFT(BA$3, 3)&lt;&gt;"Tag"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BI3:BP4">
-    <cfRule type="expression" dxfId="10" priority="9">
-      <formula>LEFT(BI$3, 3)&lt;&gt;"Tag"</formula>
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="s">
+      <formula>NOT(ISERROR(SEARCH(("s"),(AS49))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI49:BI50">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="s">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+      <formula>"i"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="s">
       <formula>NOT(ISERROR(SEARCH(("s"),(BI49))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
-      <formula>"i"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI5:BP8">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="s">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+      <formula>"i"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="s">
       <formula>NOT(ISERROR(SEARCH(("s"),(BI5))))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BI10:BP48">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"i"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BI10:BP10 BI11:BO11 BI12:BP48">
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="s">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="s">
       <formula>NOT(ISERROR(SEARCH(("s"),(BI10))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
-      <formula>"i"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BP11">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="s">
-      <formula>NOT(ISERROR(SEARCH(("s"),(BP11))))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"i"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6703,7 +6698,7 @@
       <c r="A3" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="121">
+      <c r="B3" s="55">
         <v>46084</v>
       </c>
       <c r="C3" s="40"/>
